--- a/backend/seed_data.xlsx
+++ b/backend/seed_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SQD-APP\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222C2D68-5B32-4B61-BEE7-BEE23EB7B2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B6C886-AFF7-4347-99AE-FEA1657B0004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{41E90314-8081-4FCF-A087-DDC2FA11651E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{41E90314-8081-4FCF-A087-DDC2FA11651E}"/>
   </bookViews>
   <sheets>
     <sheet name="GUIDE" sheetId="1" r:id="rId1"/>
@@ -1016,7 +1016,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9794" uniqueCount="3460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9820" uniqueCount="3466">
   <si>
     <t>Sheet</t>
   </si>
@@ -11541,6 +11541,24 @@
   </si>
   <si>
     <t>Material Control Error</t>
+  </si>
+  <si>
+    <t>BP-4</t>
+  </si>
+  <si>
+    <t>BP-5</t>
+  </si>
+  <si>
+    <t>BP-6</t>
+  </si>
+  <si>
+    <t>INVESTIGATION - L2</t>
+  </si>
+  <si>
+    <t>OPS/CAP APPROVAL - RENEWAL</t>
+  </si>
+  <si>
+    <t>INVESTIGATION - L1</t>
   </si>
 </sst>
 </file>
@@ -49896,13 +49914,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="20.8984375" style="2" customWidth="1"/>
     <col min="3" max="3" width="22.3984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -49976,13 +49994,10 @@
         <v>7</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>396</v>
@@ -50020,7 +50035,7 @@
         <v>391</v>
       </c>
       <c r="G3" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>392</v>
@@ -50029,7 +50044,7 @@
         <v>412</v>
       </c>
       <c r="J3" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>2229</v>
@@ -50091,10 +50106,101 @@
         <v>396</v>
       </c>
     </row>
+    <row r="5" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>3464</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>3447</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>3461</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="78" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>2708</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:O1 A4 A2 D2 A3 F3:J3 F2:K2 E4:K4 N3:O3 N4:O4 M2:O2 L3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:O1 A4 A2 D2 A3 F3 F2:G2 E4:K4 N3:O3 N4:O4 M2:O2 L3 H3:I3 K2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
